--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-family-member-history.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-family-member-history.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$59</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="375">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>FamilyMemberHistory - Fr FamilyMemberHistory</t>
+    <t>FamilyMemberHistory - Fr Antécédents familiaux</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -599,7 +599,7 @@
 </t>
   </si>
   <si>
-    <t>Patient history is about</t>
+    <t>Patient concerné</t>
   </si>
   <si>
     <t>The person who this history concerns.</t>
@@ -850,7 +850,7 @@
 </t>
   </si>
   <si>
-    <t>Condition that the related person had</t>
+    <t>Problème</t>
   </si>
   <si>
     <t>The significant Conditions (or condition) that the family member had. This is a repeating section to allow a system to represent more than one condition per resource, though there is nothing stopping multiple resources - one per condition.</t>
@@ -903,7 +903,7 @@
 </t>
   </si>
   <si>
-    <t>Target anatomic location or structure</t>
+    <t>Localisation anatomique</t>
   </si>
   <si>
     <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
@@ -951,14 +951,151 @@
     <t>author</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-author-extension}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
 </t>
   </si>
   <si>
-    <t>Extension - Auteur</t>
-  </si>
-  <si>
-    <t>Extension permettant d’indiquer l’auteur de l’information sur la condition familiale.</t>
+    <t>Auteur</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.extension.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:reference.id</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:reference.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-document)
+</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.url</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>FamilyMemberHistory.condition.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
     <t>FamilyMemberHistory.condition.modifierExtension</t>
@@ -1362,11 +1499,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN40"/>
+  <dimension ref="A1:AN59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.50390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.19140625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.48828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="11.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1375,7 +1512,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="152.35546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1393,7 +1530,7 @@
     <col min="26" max="26" width="68.7890625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="42.19140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4843,7 +4980,7 @@
         <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -4957,7 +5094,7 @@
         <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
@@ -5071,7 +5208,7 @@
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5185,7 +5322,7 @@
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5283,43 +5420,39 @@
         <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5367,19 +5500,19 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5388,7 +5521,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>131</v>
+        <v>274</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5396,10 +5529,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5407,13 +5540,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>306</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>77</v>
@@ -5422,13 +5555,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5455,41 +5588,43 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
@@ -5498,7 +5633,7 @@
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>311</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5506,12 +5641,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
       </c>
@@ -5523,7 +5660,7 @@
         <v>88</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -5532,13 +5669,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>313</v>
+        <v>276</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5565,13 +5702,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>316</v>
+        <v>77</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5589,19 +5726,19 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>312</v>
+        <v>280</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
@@ -5610,7 +5747,7 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5618,10 +5755,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5644,13 +5781,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>319</v>
+        <v>271</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>320</v>
+        <v>272</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5701,7 +5838,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>273</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5713,7 +5850,7 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -5722,7 +5859,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5730,10 +5867,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5744,7 +5881,7 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -5756,18 +5893,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>322</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>277</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>325</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -5803,31 +5938,31 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>307</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5836,7 +5971,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5844,10 +5979,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5855,10 +5990,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>77</v>
@@ -5870,22 +6005,24 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>260</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>77</v>
+        <v>309</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>77</v>
@@ -5927,35 +6064,2175 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y41" s="2"/>
+      <c r="Z41" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
+      <c r="B42" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C42" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="D42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O45" s="2"/>
+      <c r="P45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="D47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y55" s="2"/>
+      <c r="Z55" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AN40" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN40">
+  <autoFilter ref="A1:AN59">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5965,7 +8242,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI39">
+  <conditionalFormatting sqref="A2:AI58">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-family-member-history.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-family-member-history.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
